--- a/artfynd/A 20626-2026 artfynd.xlsx
+++ b/artfynd/A 20626-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116049662</v>
+        <v>121633384</v>
       </c>
       <c r="B2" t="n">
-        <v>105301</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>1971</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Stor sotdyna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Camarops polysperma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Mont.) J.H.Mill.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skogssäter-Stenkullen-Ingelkärr, Boh</t>
+          <t>Österslätt, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>316036</v>
+        <v>316009</v>
       </c>
       <c r="R2" t="n">
-        <v>6440515</v>
+        <v>6440534</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,17 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>står nära kraftledningsgata och intill bäck. 90 cm i stamdiameter   Gammalt träd</t>
+          <t>Gammalt ex. På klibbal.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,71 +765,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sandra Johansson</t>
+          <t>Emma Håkansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sandra Johansson, Robert Petersen, Johanna Ek, Tilda Lindkvist, Jeanette Karlsson, Mathias Molau</t>
+          <t>Per Österman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121302651</v>
+        <v>121633383</v>
       </c>
       <c r="B3" t="n">
-        <v>57838</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103018</v>
+        <v>6428</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stenungsund, Boh</t>
+          <t>Österslätt, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>316029</v>
+        <v>316014</v>
       </c>
       <c r="R3" t="n">
-        <v>6440507</v>
+        <v>6440512</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,12 +842,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På grov rönn.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,7 +867,7 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Per Österman</t>
+          <t>Emma Håkansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -897,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121633383</v>
+        <v>121302651</v>
       </c>
       <c r="B4" t="n">
-        <v>74549</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,34 +890,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>103018</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Österslätt, Boh</t>
+          <t>Stenungsund, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>316014</v>
+        <v>316029</v>
       </c>
       <c r="R4" t="n">
-        <v>6440512</v>
+        <v>6440507</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,17 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På grov rönn.</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,7 +973,7 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Emma Håkansson</t>
+          <t>Per Österman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1001,6 +982,112 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>116049662</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skogssäter-Stenkullen-Ingelkärr, Boh</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>316036</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6440515</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>står nära kraftledningsgata och intill bäck. 90 cm i stamdiameter   Gammalt träd</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sandra Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sandra Johansson, Robert Petersen, Johanna Ek, Tilda Lindkvist, Jeanette Karlsson, Mathias Molau</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20626-2026 artfynd.xlsx
+++ b/artfynd/A 20626-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121633384</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121633383</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121302651</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,8 +1108,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116049662</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>